--- a/modules_schedules/Y4_B2526_General_&_Special_Internal_1_B2_schedule.xlsx
+++ b/modules_schedules/Y4_B2526_General_&_Special_Internal_1_B2_schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Desktop\modules_schedules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DACE25-1660-4E01-8AC4-05627F904E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A271B4E4-E41E-48EA-9C00-DA1111F0BFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="580" windowWidth="18280" windowHeight="13100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General_&amp;_Special_Internal_1" sheetId="1" r:id="rId1"/>
@@ -232,9 +232,6 @@
     <t>04/12/2025</t>
   </si>
   <si>
-    <t>tropical</t>
-  </si>
-  <si>
     <t>08/02/2026</t>
   </si>
   <si>
@@ -290,6 +287,9 @@
   </si>
   <si>
     <t>10/01/2026</t>
+  </si>
+  <si>
+    <t>tropical medicine</t>
   </si>
 </sst>
 </file>
@@ -1823,13 +1823,13 @@
         <v>8</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>12</v>
@@ -1846,13 +1846,13 @@
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>12</v>
@@ -1869,13 +1869,13 @@
         <v>8</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>12</v>
@@ -1892,13 +1892,13 @@
         <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>12</v>
@@ -1915,13 +1915,13 @@
         <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>12</v>
@@ -1935,7 +1935,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>9</v>
@@ -1944,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>12</v>
@@ -1958,7 +1958,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>9</v>
@@ -2004,7 +2004,7 @@
         <v>7</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
@@ -2027,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
@@ -2036,7 +2036,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>12</v>
@@ -2050,7 +2050,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>9</v>
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>9</v>
@@ -2096,7 +2096,7 @@
         <v>7</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>9</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
@@ -2142,7 +2142,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>31</v>
@@ -2165,7 +2165,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>31</v>
@@ -2188,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>31</v>
@@ -2211,7 +2211,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>31</v>
@@ -2234,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>31</v>
@@ -2243,7 +2243,7 @@
         <v>19</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>12</v>
@@ -2257,7 +2257,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>31</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>31</v>
@@ -2303,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>31</v>
@@ -2326,7 +2326,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>31</v>
@@ -2349,7 +2349,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>31</v>
@@ -2358,7 +2358,7 @@
         <v>29</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>12</v>
@@ -2372,7 +2372,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>41</v>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>41</v>
@@ -2418,7 +2418,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>41</v>
@@ -2441,7 +2441,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>41</v>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>41</v>
@@ -2487,7 +2487,7 @@
         <v>7</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>47</v>
@@ -2510,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>47</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>47</v>
@@ -2556,7 +2556,7 @@
         <v>7</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>47</v>
@@ -2579,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>53</v>
@@ -2602,7 +2602,7 @@
         <v>7</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>53</v>
@@ -2625,7 +2625,7 @@
         <v>7</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>53</v>
@@ -2648,7 +2648,7 @@
         <v>7</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>53</v>
@@ -2671,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>53</v>
@@ -2694,7 +2694,7 @@
         <v>7</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>53</v>
@@ -2717,7 +2717,7 @@
         <v>7</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>53</v>
@@ -2740,7 +2740,7 @@
         <v>7</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>53</v>
@@ -2763,7 +2763,7 @@
         <v>7</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>53</v>
@@ -2786,7 +2786,7 @@
         <v>7</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>53</v>
@@ -2809,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>59</v>
@@ -2832,7 +2832,7 @@
         <v>7</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>59</v>
@@ -2855,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>59</v>
@@ -2878,7 +2878,7 @@
         <v>7</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>59</v>
@@ -2901,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>59</v>
@@ -2924,7 +2924,7 @@
         <v>7</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>59</v>
@@ -2933,7 +2933,7 @@
         <v>21</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>12</v>
@@ -2947,7 +2947,7 @@
         <v>7</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>59</v>
@@ -2956,7 +2956,7 @@
         <v>23</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>12</v>
@@ -2970,7 +2970,7 @@
         <v>7</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>59</v>
@@ -2979,7 +2979,7 @@
         <v>25</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>12</v>
@@ -2993,7 +2993,7 @@
         <v>7</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>59</v>
@@ -3002,7 +3002,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>12</v>
@@ -3016,7 +3016,7 @@
         <v>7</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>59</v>
@@ -3025,7 +3025,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>12</v>
@@ -3039,10 +3039,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>10</v>
@@ -3062,10 +3062,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>13</v>
@@ -3085,10 +3085,10 @@
         <v>7</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>15</v>
@@ -3108,10 +3108,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>17</v>
@@ -3131,10 +3131,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>19</v>
@@ -3154,7 +3154,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>12</v>
@@ -3177,7 +3177,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>9</v>
@@ -3200,7 +3200,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
@@ -3223,7 +3223,7 @@
         <v>7</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>9</v>
@@ -3246,7 +3246,7 @@
         <v>7</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>9</v>
@@ -3255,7 +3255,7 @@
         <v>6</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>12</v>
@@ -3269,7 +3269,7 @@
         <v>7</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>9</v>
@@ -3292,7 +3292,7 @@
         <v>7</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>9</v>
@@ -3315,7 +3315,7 @@
         <v>7</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
@@ -3338,7 +3338,7 @@
         <v>7</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>9</v>
@@ -3361,7 +3361,7 @@
         <v>7</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>31</v>
@@ -3384,7 +3384,7 @@
         <v>7</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>31</v>
@@ -3407,7 +3407,7 @@
         <v>7</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>31</v>
@@ -3430,7 +3430,7 @@
         <v>7</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>31</v>
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>31</v>
@@ -3476,7 +3476,7 @@
         <v>7</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>31</v>
@@ -3499,7 +3499,7 @@
         <v>7</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>31</v>
@@ -3522,7 +3522,7 @@
         <v>7</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>31</v>
@@ -3545,7 +3545,7 @@
         <v>7</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>31</v>
@@ -3568,7 +3568,7 @@
         <v>7</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>31</v>
@@ -3591,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>41</v>
@@ -3614,7 +3614,7 @@
         <v>7</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>41</v>
@@ -3637,7 +3637,7 @@
         <v>7</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>41</v>
@@ -3646,7 +3646,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F129" s="4">
         <v>0.33333333333333331</v>
@@ -3660,7 +3660,7 @@
         <v>7</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>41</v>
@@ -3669,7 +3669,7 @@
         <v>4</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F130" s="8">
         <v>0.33333333333333331</v>
@@ -3683,7 +3683,7 @@
         <v>7</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>41</v>
@@ -3692,7 +3692,7 @@
         <v>5</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F131" s="4">
         <v>0.33333333333333331</v>
@@ -3706,7 +3706,7 @@
         <v>7</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>47</v>
@@ -3729,7 +3729,7 @@
         <v>7</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>47</v>
@@ -3752,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>47</v>
@@ -3775,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>47</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>47</v>
@@ -3807,7 +3807,7 @@
         <v>19</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>12</v>
@@ -3821,7 +3821,7 @@
         <v>7</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>53</v>
@@ -3844,7 +3844,7 @@
         <v>7</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>53</v>
@@ -3867,7 +3867,7 @@
         <v>7</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>53</v>
@@ -3890,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>53</v>
@@ -3913,7 +3913,7 @@
         <v>7</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>53</v>
@@ -3936,7 +3936,7 @@
         <v>7</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>53</v>
@@ -3945,7 +3945,7 @@
         <v>21</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F142" s="8">
         <v>0.41666666666666669</v>
@@ -3959,7 +3959,7 @@
         <v>7</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>53</v>
@@ -3968,7 +3968,7 @@
         <v>23</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F143" s="4">
         <v>0.41666666666666669</v>
@@ -3982,7 +3982,7 @@
         <v>7</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>53</v>
@@ -3991,7 +3991,7 @@
         <v>25</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F144" s="8">
         <v>0.41666666666666669</v>
@@ -4005,7 +4005,7 @@
         <v>7</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>53</v>
@@ -4014,7 +4014,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F145" s="4">
         <v>0.41666666666666669</v>
@@ -4028,7 +4028,7 @@
         <v>7</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>53</v>
@@ -4037,7 +4037,7 @@
         <v>29</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F146" s="8">
         <v>0.41666666666666669</v>
@@ -4051,7 +4051,7 @@
         <v>7</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>59</v>
@@ -4074,7 +4074,7 @@
         <v>7</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>59</v>
@@ -4097,7 +4097,7 @@
         <v>7</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>59</v>
@@ -4120,7 +4120,7 @@
         <v>7</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>59</v>
@@ -4143,7 +4143,7 @@
         <v>7</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>59</v>
@@ -4166,7 +4166,7 @@
         <v>7</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>59</v>
@@ -4189,7 +4189,7 @@
         <v>7</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>59</v>
@@ -4212,7 +4212,7 @@
         <v>7</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>59</v>
@@ -4235,7 +4235,7 @@
         <v>7</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>59</v>
@@ -4258,10 +4258,10 @@
         <v>7</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>10</v>
@@ -4281,10 +4281,10 @@
         <v>7</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>13</v>
@@ -4304,10 +4304,10 @@
         <v>7</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>15</v>
@@ -4327,10 +4327,10 @@
         <v>7</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>17</v>
@@ -4350,16 +4350,16 @@
         <v>7</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>12</v>
@@ -4373,7 +4373,7 @@
         <v>7</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>9</v>
@@ -4382,7 +4382,7 @@
         <v>21</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>12</v>
@@ -4396,7 +4396,7 @@
         <v>7</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>9</v>
@@ -4419,7 +4419,7 @@
         <v>7</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>9</v>
@@ -4442,7 +4442,7 @@
         <v>7</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>9</v>
@@ -4465,7 +4465,7 @@
         <v>7</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>9</v>
@@ -4488,7 +4488,7 @@
         <v>7</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>9</v>
@@ -4497,7 +4497,7 @@
         <v>10</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>12</v>
@@ -4511,7 +4511,7 @@
         <v>7</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>9</v>
@@ -4520,7 +4520,7 @@
         <v>13</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>12</v>
@@ -4534,7 +4534,7 @@
         <v>7</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>9</v>
@@ -4543,7 +4543,7 @@
         <v>15</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>12</v>
@@ -4557,7 +4557,7 @@
         <v>7</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>9</v>
@@ -4566,7 +4566,7 @@
         <v>17</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>12</v>
@@ -4580,7 +4580,7 @@
         <v>7</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>31</v>
@@ -4603,7 +4603,7 @@
         <v>7</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>31</v>
@@ -4626,7 +4626,7 @@
         <v>7</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>31</v>
@@ -4649,7 +4649,7 @@
         <v>7</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>31</v>
@@ -4672,7 +4672,7 @@
         <v>7</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>31</v>
@@ -4695,7 +4695,7 @@
         <v>7</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>31</v>
@@ -4718,7 +4718,7 @@
         <v>7</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>31</v>
@@ -4741,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>31</v>
@@ -4764,7 +4764,7 @@
         <v>7</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>31</v>
@@ -4787,7 +4787,7 @@
         <v>7</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>31</v>
@@ -4810,7 +4810,7 @@
         <v>7</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>41</v>
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>41</v>
@@ -4856,7 +4856,7 @@
         <v>7</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>41</v>
@@ -4879,7 +4879,7 @@
         <v>7</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>41</v>
@@ -4902,7 +4902,7 @@
         <v>7</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>47</v>
@@ -4925,7 +4925,7 @@
         <v>7</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>47</v>
@@ -4948,7 +4948,7 @@
         <v>7</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>47</v>
@@ -4971,7 +4971,7 @@
         <v>7</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>47</v>
@@ -4994,7 +4994,7 @@
         <v>7</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>47</v>
@@ -5017,7 +5017,7 @@
         <v>7</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>53</v>
@@ -5040,7 +5040,7 @@
         <v>7</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>53</v>
@@ -5063,7 +5063,7 @@
         <v>7</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>53</v>
@@ -5086,7 +5086,7 @@
         <v>7</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>53</v>
@@ -5109,7 +5109,7 @@
         <v>7</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>53</v>
@@ -5132,7 +5132,7 @@
         <v>7</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>53</v>
@@ -5155,7 +5155,7 @@
         <v>7</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>53</v>
@@ -5178,7 +5178,7 @@
         <v>7</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>53</v>
@@ -5201,7 +5201,7 @@
         <v>7</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>53</v>
@@ -5224,7 +5224,7 @@
         <v>7</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>59</v>
@@ -5247,7 +5247,7 @@
         <v>7</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>59</v>
@@ -5270,7 +5270,7 @@
         <v>7</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>59</v>
@@ -5293,7 +5293,7 @@
         <v>7</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>59</v>
@@ -5316,7 +5316,7 @@
         <v>7</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>59</v>
@@ -5325,7 +5325,7 @@
         <v>19</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F202" s="8" t="s">
         <v>12</v>
@@ -5339,7 +5339,7 @@
         <v>7</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>59</v>
@@ -5362,7 +5362,7 @@
         <v>7</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>59</v>
@@ -5385,7 +5385,7 @@
         <v>7</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>59</v>
@@ -5408,7 +5408,7 @@
         <v>7</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>59</v>
@@ -5431,7 +5431,7 @@
         <v>7</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>59</v>
@@ -5440,7 +5440,7 @@
         <v>29</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>12</v>
@@ -5454,10 +5454,10 @@
         <v>7</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>10</v>
@@ -5477,10 +5477,10 @@
         <v>7</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>13</v>
@@ -5500,10 +5500,10 @@
         <v>7</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>15</v>
@@ -5523,10 +5523,10 @@
         <v>7</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>17</v>
@@ -5546,10 +5546,10 @@
         <v>7</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>19</v>
@@ -5569,7 +5569,7 @@
         <v>7</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>9</v>
@@ -5578,7 +5578,7 @@
         <v>10</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>12</v>
@@ -5592,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>9</v>
@@ -5615,7 +5615,7 @@
         <v>7</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>9</v>
@@ -5638,7 +5638,7 @@
         <v>7</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>9</v>
@@ -5661,7 +5661,7 @@
         <v>7</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>9</v>
@@ -5670,7 +5670,7 @@
         <v>21</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F217" s="8" t="s">
         <v>12</v>
@@ -5684,7 +5684,7 @@
         <v>7</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>9</v>
@@ -5707,7 +5707,7 @@
         <v>7</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>9</v>
@@ -5730,7 +5730,7 @@
         <v>7</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>9</v>
@@ -5753,7 +5753,7 @@
         <v>7</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>9</v>
@@ -5776,7 +5776,7 @@
         <v>7</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>31</v>
@@ -5799,7 +5799,7 @@
         <v>7</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>31</v>
@@ -5822,7 +5822,7 @@
         <v>7</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>31</v>
@@ -5845,7 +5845,7 @@
         <v>7</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>31</v>
@@ -5868,7 +5868,7 @@
         <v>7</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>31</v>
@@ -5891,7 +5891,7 @@
         <v>7</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>31</v>
@@ -5900,7 +5900,7 @@
         <v>21</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F227" s="8" t="s">
         <v>12</v>
@@ -5914,7 +5914,7 @@
         <v>7</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>31</v>
@@ -5923,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>12</v>
@@ -5937,7 +5937,7 @@
         <v>7</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>31</v>
@@ -5946,7 +5946,7 @@
         <v>25</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F229" s="8" t="s">
         <v>12</v>
@@ -5960,7 +5960,7 @@
         <v>7</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>31</v>
@@ -5969,7 +5969,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>12</v>
@@ -5983,7 +5983,7 @@
         <v>7</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>31</v>
@@ -5992,7 +5992,7 @@
         <v>29</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F231" s="8" t="s">
         <v>12</v>
@@ -6006,7 +6006,7 @@
         <v>7</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>41</v>
@@ -6029,7 +6029,7 @@
         <v>7</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>41</v>
@@ -6052,7 +6052,7 @@
         <v>7</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>41</v>
@@ -6075,7 +6075,7 @@
         <v>7</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>41</v>
@@ -6098,7 +6098,7 @@
         <v>7</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>41</v>
@@ -6107,7 +6107,7 @@
         <v>19</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F236" s="4">
         <v>0.33333333333333331</v>
@@ -6121,7 +6121,7 @@
         <v>7</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>47</v>
@@ -6144,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>47</v>
@@ -6167,7 +6167,7 @@
         <v>7</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>47</v>
@@ -6190,7 +6190,7 @@
         <v>7</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>47</v>
@@ -6213,7 +6213,7 @@
         <v>7</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>47</v>
@@ -6236,7 +6236,7 @@
         <v>7</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>53</v>
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>53</v>
@@ -6282,7 +6282,7 @@
         <v>7</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>53</v>
@@ -6305,7 +6305,7 @@
         <v>7</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C245" s="6" t="s">
         <v>53</v>
@@ -6328,7 +6328,7 @@
         <v>7</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>53</v>
@@ -6337,7 +6337,7 @@
         <v>19</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F246" s="4">
         <v>0.41666666666666669</v>
@@ -6351,7 +6351,7 @@
         <v>7</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C247" s="6" t="s">
         <v>53</v>
@@ -6374,7 +6374,7 @@
         <v>7</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>53</v>
@@ -6397,7 +6397,7 @@
         <v>7</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>53</v>
@@ -6420,7 +6420,7 @@
         <v>7</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>53</v>
@@ -6443,7 +6443,7 @@
         <v>7</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C251" s="6" t="s">
         <v>53</v>
@@ -6452,7 +6452,7 @@
         <v>29</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F251" s="8">
         <v>0.41666666666666669</v>
@@ -6466,7 +6466,7 @@
         <v>7</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>59</v>
@@ -6489,7 +6489,7 @@
         <v>7</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C253" s="6" t="s">
         <v>59</v>
@@ -6512,7 +6512,7 @@
         <v>7</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>59</v>
@@ -6535,7 +6535,7 @@
         <v>7</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C255" s="6" t="s">
         <v>59</v>
@@ -6558,7 +6558,7 @@
         <v>7</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>59</v>
@@ -6581,7 +6581,7 @@
         <v>7</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C257" s="6" t="s">
         <v>59</v>
@@ -6604,7 +6604,7 @@
         <v>7</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>59</v>
@@ -6627,7 +6627,7 @@
         <v>7</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>59</v>
@@ -6650,7 +6650,7 @@
         <v>7</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>59</v>
@@ -6673,7 +6673,7 @@
         <v>7</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C261" s="6" t="s">
         <v>59</v>
@@ -6696,10 +6696,10 @@
         <v>7</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>10</v>
@@ -6719,10 +6719,10 @@
         <v>7</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D263" s="6" t="s">
         <v>13</v>
@@ -6742,10 +6742,10 @@
         <v>7</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>15</v>
@@ -6765,10 +6765,10 @@
         <v>7</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D265" s="6" t="s">
         <v>17</v>
@@ -6788,10 +6788,10 @@
         <v>7</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>19</v>
